--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -1,25 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GF_X\AAAGameData\DataTables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="2775" windowWidth="25860" windowHeight="14685"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>#</t>
   </si>
@@ -33,10 +41,16 @@
     <t>LvPfbName</t>
   </si>
   <si>
-    <t>InitMoney</t>
-  </si>
-  <si>
-    <t>MoneyColorId</t>
+    <t>SlotCount</t>
+  </si>
+  <si>
+    <t>FishCount</t>
+  </si>
+  <si>
+    <t>RepeatCount</t>
+  </si>
+  <si>
+    <t>Layers</t>
   </si>
   <si>
     <t>int</t>
@@ -45,72 +59,47 @@
     <t>string</t>
   </si>
   <si>
+    <t>float[][]</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
     <t>关卡prefab名</t>
   </si>
   <si>
-    <t>玩家初始钱数</t>
-  </si>
-  <si>
-    <t>取值1-6</t>
+    <t>初始槽数</t>
+  </si>
+  <si>
+    <t>鱼数量</t>
+  </si>
+  <si>
+    <t>每种小猫卡片出现的次数</t>
+  </si>
+  <si>
+    <t>小猫堆配置，每个数组表示一层，数组第一个元素为列数，第二个元素为行数，第三个元素为相对下面一层的水平偏移（0.5表示错开半格，0表示对齐，1表示偏移1格），第四个元素为相对下面一层的垂直偏移</t>
   </si>
   <si>
     <t>Lv_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LvDisplayName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tring</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level.DisplayName1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level.DisplayName2</t>
-  </si>
-  <si>
-    <t>Level.DisplayName3</t>
-  </si>
-  <si>
-    <t>Level.DisplayName4</t>
-  </si>
-  <si>
-    <t>Level.DisplayName5</t>
-  </si>
-  <si>
-    <t>关卡显示名(多语言)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i18n</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2,2,0,0],[2,2,0,0],[2,2,0,0]</t>
+  </si>
+  <si>
+    <t>[2,2,0.5,0.5],[2,2,0.5,0.5],[2,2,0.5,0.5]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,38 +108,355 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="4"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -158,26 +464,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -435,36 +1027,34 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
     <col min="3" max="3" width="5.125" customWidth="1"/>
     <col min="4" max="4" width="15.5" customWidth="1"/>
     <col min="5" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="24.1666666666667" customWidth="1"/>
+    <col min="8" max="8" width="33.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -481,137 +1071,157 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" ht="14.5" spans="1:8">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" ht="14.5" spans="2:8">
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
+      <c r="D5" t="s">
+        <v>17</v>
       </c>
       <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
         <v>200</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>15</v>
+      <c r="G5" s="1">
+        <v>6</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" ht="14.5" spans="2:8">
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
+      <c r="D6" t="s">
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>200</v>
+      </c>
+      <c r="G6" s="1">
+        <v>6</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" ht="14.5" spans="2:7">
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>12</v>
+      <c r="D7" t="s">
+        <v>17</v>
       </c>
       <c r="E7">
-        <v>315</v>
+        <v>5</v>
       </c>
       <c r="F7">
+        <v>200</v>
+      </c>
+      <c r="G7" s="1">
         <v>6</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" ht="14.5" spans="2:7">
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
+      <c r="D8" t="s">
+        <v>17</v>
       </c>
       <c r="E8">
-        <v>210</v>
+        <v>5</v>
       </c>
       <c r="F8">
+        <v>200</v>
+      </c>
+      <c r="G8" s="1">
         <v>6</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" ht="14.5" spans="2:7">
       <c r="B9">
         <v>5</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>12</v>
+      <c r="D9" t="s">
+        <v>17</v>
       </c>
       <c r="E9">
-        <v>315</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>3</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>19</v>
+        <v>200</v>
+      </c>
+      <c r="G9" s="1">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="D3:H3">
+      <formula1>"int,bool,enum,double,string[],string,float,uint,short,Vector4,Vector2,Vector3Int,Vector3,Color,Color32,Vector3[],Vector2Int,int[],float[],bool[],double[],ushort,ulong,int[][],double[][],decimal,long,float[][],bool[][],Rect,Quaternion,DateTime,sbyte,char"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -83,7 +83,7 @@
     <t>Lv_1</t>
   </si>
   <si>
-    <t>[2,2,0,0],[2,2,0,0],[2,2,0,0]</t>
+    <t>[4,4,0,0],[4,4,0,0],[4,4,0,0]</t>
   </si>
   <si>
     <t>[2,2,0.5,0.5],[2,2,0.5,0.5],[2,2,0.5,0.5]</t>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
   <si>
     <t>#</t>
   </si>
@@ -59,7 +59,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>float[][]</t>
+    <t>int[]</t>
   </si>
   <si>
     <t>备注</t>
@@ -77,16 +77,16 @@
     <t>每种小猫卡片出现的次数</t>
   </si>
   <si>
-    <t>小猫堆配置，每个数组表示一层，数组第一个元素为列数，第二个元素为行数，第三个元素为相对下面一层的水平偏移（0.5表示错开半格，0表示对齐，1表示偏移1格），第四个元素为相对下面一层的垂直偏移</t>
+    <t>小猫堆配置，读取LayerTable表数据，1,2,3表示第一层用id为1，第二层用id为2，第三层用id为3的层配置堆叠成小猫堆</t>
   </si>
   <si>
     <t>Lv_1</t>
   </si>
   <si>
-    <t>[4,4,0,0],[4,4,0,0],[4,4,0,0]</t>
-  </si>
-  <si>
-    <t>[2,2,0.5,0.5],[2,2,0.5,0.5],[2,2,0.5,0.5]</t>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
   </si>
 </sst>
 </file>
@@ -99,7 +99,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,11 +110,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -580,140 +575,139 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1093,7 +1087,7 @@
       <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -1163,7 +1157,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" ht="14.5" spans="2:7">
+    <row r="7" ht="14.5" spans="2:8">
       <c r="B7">
         <v>3</v>
       </c>
@@ -1179,8 +1173,11 @@
       <c r="G7" s="1">
         <v>6</v>
       </c>
+      <c r="H7" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="8" ht="14.5" spans="2:7">
+    <row r="8" ht="14.5" spans="2:8">
       <c r="B8">
         <v>4</v>
       </c>
@@ -1196,8 +1193,11 @@
       <c r="G8" s="1">
         <v>6</v>
       </c>
+      <c r="H8" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="9" ht="14.5" spans="2:7">
+    <row r="9" ht="14.5" spans="2:8">
       <c r="B9">
         <v>5</v>
       </c>
@@ -1212,6 +1212,9 @@
       </c>
       <c r="G9" s="1">
         <v>6</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
   <si>
     <t>#</t>
   </si>
@@ -81,9 +81,6 @@
   </si>
   <si>
     <t>Lv_1</t>
-  </si>
-  <si>
-    <t>1,2</t>
   </si>
   <si>
     <t>1,2,3</t>
@@ -1154,7 +1151,7 @@
         <v>6</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" ht="14.5" spans="2:8">
@@ -1174,7 +1171,7 @@
         <v>6</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" ht="14.5" spans="2:8">
@@ -1194,7 +1191,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" ht="14.5" spans="2:8">
@@ -1214,7 +1211,7 @@
         <v>6</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
   <si>
     <t>#</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Lv_1</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
   </si>
   <si>
     <t>1,2,3</t>
@@ -1122,7 +1125,7 @@
         <v>17</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>200</v>
@@ -1151,7 +1154,7 @@
         <v>6</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="14.5" spans="2:8">
@@ -1171,7 +1174,7 @@
         <v>6</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="14.5" spans="2:8">
@@ -1191,7 +1194,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="14.5" spans="2:8">
@@ -1211,7 +1214,7 @@
         <v>6</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
   <si>
     <t>#</t>
   </si>
@@ -47,9 +47,6 @@
     <t>FishCount</t>
   </si>
   <si>
-    <t>RepeatCount</t>
-  </si>
-  <si>
     <t>Layers</t>
   </si>
   <si>
@@ -72,9 +69,6 @@
   </si>
   <si>
     <t>鱼数量</t>
-  </si>
-  <si>
-    <t>每种小猫卡片出现的次数</t>
   </si>
   <si>
     <t>小猫堆配置，读取LayerTable表数据，1,2,3表示第一层用id为1，第二层用id为2，第三层用id为3的层配置堆叠成小猫堆</t>
@@ -1027,8 +1021,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
@@ -1036,8 +1030,7 @@
     <col min="4" max="4" width="15.5" customWidth="1"/>
     <col min="5" max="5" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
-    <col min="7" max="7" width="24.1666666666667" customWidth="1"/>
-    <col min="8" max="8" width="33.75" customWidth="1"/>
+    <col min="7" max="7" width="33.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1048,7 +1041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1067,62 +1060,53 @@
       <c r="G2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="3" ht="14.5" spans="1:8">
+    <row r="3" ht="14.5" spans="1:7">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="5" ht="14.5" spans="2:8">
+    <row r="5" ht="14.5" spans="2:7">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -1130,19 +1114,16 @@
       <c r="F5">
         <v>200</v>
       </c>
-      <c r="G5" s="1">
-        <v>6</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>18</v>
+      <c r="G5" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="6" ht="14.5" spans="2:8">
+    <row r="6" ht="14.5" spans="2:7">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1150,19 +1131,16 @@
       <c r="F6">
         <v>200</v>
       </c>
-      <c r="G6" s="1">
-        <v>6</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>19</v>
+      <c r="G6" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="7" ht="14.5" spans="2:8">
+    <row r="7" ht="14.5" spans="2:7">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1170,19 +1148,16 @@
       <c r="F7">
         <v>200</v>
       </c>
-      <c r="G7" s="1">
-        <v>6</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>19</v>
+      <c r="G7" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="8" ht="14.5" spans="2:8">
+    <row r="8" ht="14.5" spans="2:7">
       <c r="B8">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1190,19 +1165,16 @@
       <c r="F8">
         <v>200</v>
       </c>
-      <c r="G8" s="1">
-        <v>6</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>19</v>
+      <c r="G8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="9" ht="14.5" spans="2:8">
+    <row r="9" ht="14.5" spans="2:7">
       <c r="B9">
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9">
         <v>5</v>
@@ -1210,16 +1182,13 @@
       <c r="F9">
         <v>200</v>
       </c>
-      <c r="G9" s="1">
-        <v>6</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>19</v>
+      <c r="G9" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D3:H3">
+    <dataValidation type="list" sqref="D3:G3">
       <formula1>"int,bool,enum,double,string[],string,float,uint,short,Vector4,Vector2,Vector3Int,Vector3,Color,Color32,Vector3[],Vector2Int,int[],float[],bool[],double[],ushort,ulong,int[][],double[][],decimal,long,float[][],bool[][],Rect,Quaternion,DateTime,sbyte,char"</formula1>
     </dataValidation>
   </dataValidations>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t>#</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>1,1,1</t>
+  </si>
+  <si>
+    <t>1,12,18,23,24,4</t>
   </si>
   <si>
     <t>1,2,3</t>
@@ -1149,7 +1152,7 @@
         <v>200</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" ht="14.5" spans="2:7">
@@ -1166,7 +1169,7 @@
         <v>200</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" ht="14.5" spans="2:7">
@@ -1183,7 +1186,7 @@
         <v>200</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -77,7 +77,7 @@
     <t>Lv_1</t>
   </si>
   <si>
-    <t>1,1,1</t>
+    <t>2,3,4</t>
   </si>
   <si>
     <t>1,12,18,23,24,4</t>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
   <si>
     <t>#</t>
   </si>
@@ -50,6 +50,9 @@
     <t>Layers</t>
   </si>
   <si>
+    <t>CatTypes</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -74,13 +77,19 @@
     <t>小猫堆配置，读取LayerTable表数据，1,2,3表示第一层用id为1，第二层用id为2，第三层用id为3的层配置堆叠成小猫堆</t>
   </si>
   <si>
+    <t>每层小猫种类配置</t>
+  </si>
+  <si>
     <t>Lv_1</t>
   </si>
   <si>
     <t>2,3,4</t>
   </si>
   <si>
-    <t>1,12,18,23,24,4</t>
+    <t>4,3,2</t>
+  </si>
+  <si>
+    <t>1,18,18,23,24</t>
   </si>
   <si>
     <t>1,2,3</t>
@@ -1024,8 +1033,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
@@ -1044,7 +1053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1063,53 +1072,62 @@
       <c r="G2" t="s">
         <v>6</v>
       </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" ht="14.5" spans="1:7">
+    <row r="3" ht="14.5" spans="1:8">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="5" ht="14.5" spans="2:7">
+    <row r="5" ht="14.5" spans="2:8">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -1118,15 +1136,18 @@
         <v>200</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="6" ht="14.5" spans="2:7">
+    <row r="6" ht="14.5" spans="2:8">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1135,15 +1156,18 @@
         <v>200</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="7" ht="14.5" spans="2:7">
+    <row r="7" ht="14.5" spans="2:8">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1152,15 +1176,18 @@
         <v>200</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="8" ht="14.5" spans="2:7">
+    <row r="8" ht="14.5" spans="2:8">
       <c r="B8">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1169,15 +1196,18 @@
         <v>200</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="9" ht="14.5" spans="2:7">
+    <row r="9" ht="14.5" spans="2:8">
       <c r="B9">
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E9">
         <v>5</v>
@@ -1186,12 +1216,35 @@
         <v>200</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" ht="14.5" spans="2:8">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>200</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D3:G3">
+    <dataValidation type="list" sqref="D3:G3 H3">
       <formula1>"int,bool,enum,double,string[],string,float,uint,short,Vector4,Vector2,Vector3Int,Vector3,Color,Color32,Vector3[],Vector2Int,int[],float[],bool[],double[],ushort,ulong,int[][],double[][],decimal,long,float[][],bool[][],Rect,Quaternion,DateTime,sbyte,char"</formula1>
     </dataValidation>
   </dataValidations>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
   <si>
     <t>#</t>
   </si>
@@ -77,7 +77,7 @@
     <t>小猫堆配置，读取LayerTable表数据，1,2,3表示第一层用id为1，第二层用id为2，第三层用id为3的层配置堆叠成小猫堆</t>
   </si>
   <si>
-    <t>每层小猫种类配置</t>
+    <t>每层小猫种类数量配置（用于难度调节）</t>
   </si>
   <si>
     <t>Lv_1</t>
@@ -89,7 +89,10 @@
     <t>4,3,2</t>
   </si>
   <si>
-    <t>1,18,18,23,24</t>
+    <t>1,18</t>
+  </si>
+  <si>
+    <t>4,3</t>
   </si>
   <si>
     <t>1,2,3</t>
@@ -1159,7 +1162,7 @@
         <v>20</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" ht="14.5" spans="2:8">
@@ -1176,7 +1179,7 @@
         <v>200</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>19</v>
@@ -1196,7 +1199,7 @@
         <v>200</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>19</v>
@@ -1216,7 +1219,7 @@
         <v>200</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>19</v>
@@ -1244,7 +1247,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D3:G3 H3">
+    <dataValidation type="list" sqref="D3:H3">
       <formula1>"int,bool,enum,double,string[],string,float,uint,short,Vector4,Vector2,Vector3Int,Vector3,Color,Color32,Vector3[],Vector2Int,int[],float[],bool[],double[],ushort,ulong,int[][],double[][],decimal,long,float[][],bool[][],Rect,Quaternion,DateTime,sbyte,char"</formula1>
     </dataValidation>
   </dataValidations>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
   <si>
     <t>#</t>
   </si>
@@ -41,6 +41,9 @@
     <t>LvPfbName</t>
   </si>
   <si>
+    <t>LvEntityName</t>
+  </si>
+  <si>
     <t>SlotCount</t>
   </si>
   <si>
@@ -68,6 +71,9 @@
     <t>关卡prefab名</t>
   </si>
   <si>
+    <t>关卡实体类名</t>
+  </si>
+  <si>
     <t>初始槽数</t>
   </si>
   <si>
@@ -83,6 +89,9 @@
     <t>Lv_1</t>
   </si>
   <si>
+    <t>LevelEntity</t>
+  </si>
+  <si>
     <t>2,3,4</t>
   </si>
   <si>
@@ -96,6 +105,9 @@
   </si>
   <si>
     <t>1,2,3</t>
+  </si>
+  <si>
+    <t>Lv_2</t>
   </si>
 </sst>
 </file>
@@ -1036,16 +1048,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
     <col min="3" max="3" width="5.125" customWidth="1"/>
-    <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="17.5" customWidth="1"/>
-    <col min="7" max="7" width="33.75" customWidth="1"/>
+    <col min="4" max="5" width="15.5" customWidth="1"/>
+    <col min="6" max="6" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="33.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1056,7 +1068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1078,176 +1090,203 @@
       <c r="H2" t="s">
         <v>7</v>
       </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" ht="14.5" spans="1:8">
+    <row r="3" ht="14.5" spans="1:9">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5" ht="14.5" spans="2:8">
+    <row r="5" ht="14.5" spans="2:9">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5">
         <v>6</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>200</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H5" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="6" ht="14.5" spans="2:8">
+    <row r="6" ht="14.5" spans="2:9">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6">
         <v>5</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>200</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="7" ht="14.5" spans="2:8">
+    <row r="7" ht="14.5" spans="2:9">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7">
         <v>5</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>200</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="8" ht="14.5" spans="2:8">
+    <row r="8" ht="14.5" spans="2:9">
       <c r="B8">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8">
         <v>5</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>200</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="9" ht="14.5" spans="2:8">
+    <row r="9" ht="14.5" spans="2:9">
       <c r="B9">
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9">
         <v>5</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>200</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="10" ht="14.5" spans="2:8">
+    <row r="10" ht="14.5" spans="2:9">
       <c r="B10">
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10">
         <v>5</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>200</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>1</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>19</v>
+      <c r="I10" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D3:H3">
+    <dataValidation type="list" sqref="D3 E3 F3:I3">
       <formula1>"int,bool,enum,double,string[],string,float,uint,short,Vector4,Vector2,Vector3Int,Vector3,Color,Color32,Vector3[],Vector2Int,int[],float[],bool[],double[],ushort,ulong,int[][],double[][],decimal,long,float[][],bool[][],Rect,Quaternion,DateTime,sbyte,char"</formula1>
     </dataValidation>
   </dataValidations>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
   <si>
     <t>#</t>
   </si>
@@ -86,28 +86,22 @@
     <t>每层小猫种类数量配置（用于难度调节）</t>
   </si>
   <si>
+    <t>Lv_2</t>
+  </si>
+  <si>
+    <t>LevelEntity</t>
+  </si>
+  <si>
+    <t>1001,1002,1003</t>
+  </si>
+  <si>
+    <t>4,3,2</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
     <t>Lv_1</t>
-  </si>
-  <si>
-    <t>LevelEntity</t>
-  </si>
-  <si>
-    <t>2,3,4</t>
-  </si>
-  <si>
-    <t>4,3,2</t>
-  </si>
-  <si>
-    <t>1,18</t>
-  </si>
-  <si>
-    <t>4,3</t>
-  </si>
-  <si>
-    <t>1,2,3</t>
-  </si>
-  <si>
-    <t>Lv_2</t>
   </si>
 </sst>
 </file>
@@ -726,9 +720,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1162,7 +1157,7 @@
       <c r="G5">
         <v>200</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -1189,7 +1184,7 @@
         <v>23</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="14.5" spans="2:9">
@@ -1197,7 +1192,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
@@ -1209,7 +1204,7 @@
         <v>200</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>22</v>
@@ -1220,7 +1215,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -1232,7 +1227,7 @@
         <v>200</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>22</v>
@@ -1243,7 +1238,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -1255,7 +1250,7 @@
         <v>200</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>22</v>
@@ -1266,7 +1261,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -1280,13 +1275,13 @@
       <c r="H10">
         <v>1</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>22</v>
+      <c r="I10" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D3 E3 F3:I3">
+    <dataValidation type="list" sqref="D3:I3">
       <formula1>"int,bool,enum,double,string[],string,float,uint,short,Vector4,Vector2,Vector3Int,Vector3,Color,Color32,Vector3[],Vector2Int,int[],float[],bool[],double[],ushort,ulong,int[][],double[][],decimal,long,float[][],bool[][],Rect,Quaternion,DateTime,sbyte,char"</formula1>
     </dataValidation>
   </dataValidations>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t>#</t>
   </si>
@@ -92,13 +92,16 @@
     <t>LevelEntity</t>
   </si>
   <si>
-    <t>1001,1002,1003</t>
+    <t>1001,2002,1018,2012,1028,2022,1038,1001,2002,1018,2012,1028,2022,1038,1001,2002,1018,2012,1028,2022,1038,1001,2002,1018,2012,1028,2022,1038</t>
+  </si>
+  <si>
+    <t>4,3,2,3,2,2,1,4,3,2,3,2,2,1,4,3,2,3,2,2,1,4,3,2,3,2,2,1,4,3,2,3,2,2,1</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
   </si>
   <si>
     <t>4,3,2</t>
-  </si>
-  <si>
-    <t>1,2,3</t>
   </si>
   <si>
     <t>Lv_1</t>
@@ -721,9 +724,9 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1184,7 +1187,7 @@
         <v>23</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="14.5" spans="2:9">
@@ -1192,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
@@ -1207,7 +1210,7 @@
         <v>23</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="14.5" spans="2:9">
@@ -1230,7 +1233,7 @@
         <v>23</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" ht="14.5" spans="2:9">
@@ -1253,7 +1256,7 @@
         <v>23</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" ht="14.5" spans="2:9">

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
   <si>
     <t>#</t>
   </si>
@@ -92,19 +92,25 @@
     <t>LevelEntity</t>
   </si>
   <si>
-    <t>1001,2002,1018,2012,1028,2022,1038,1001,2002,1018,2012,1028,2022,1038,1001,2002,1018,2012,1028,2022,1038,1001,2002,1018,2012,1028,2022,1038</t>
-  </si>
-  <si>
-    <t>4,3,2,3,2,2,1,4,3,2,3,2,2,1,4,3,2,3,2,2,1,4,3,2,3,2,2,1,4,3,2,3,2,2,1</t>
+    <t>1040,1042,1040,1042,1040,1042,1040,1042,1040,1042,1040,1042</t>
+  </si>
+  <si>
+    <t>6,6,6,6,6,6,6,6,6,6,6,6,6,6</t>
+  </si>
+  <si>
+    <t>2025,1040,1042,1040,1042,1040,1042</t>
+  </si>
+  <si>
+    <t>6,6,6,6,6,6,6</t>
+  </si>
+  <si>
+    <t>Lv_1</t>
   </si>
   <si>
     <t>1,2,3</t>
   </si>
   <si>
     <t>4,3,2</t>
-  </si>
-  <si>
-    <t>Lv_1</t>
   </si>
 </sst>
 </file>
@@ -117,13 +123,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -593,140 +604,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1055,7 +1067,8 @@
     <col min="4" max="5" width="15.5" customWidth="1"/>
     <col min="6" max="6" width="14.125" customWidth="1"/>
     <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="33.75" customWidth="1"/>
+    <col min="8" max="8" width="106.25" customWidth="1"/>
+    <col min="9" max="9" width="37.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1144,7 +1157,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" ht="14.5" spans="2:9">
+    <row r="5" customFormat="1" ht="14.5" spans="2:9">
       <c r="B5">
         <v>1</v>
       </c>
@@ -1163,11 +1176,11 @@
       <c r="H5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" ht="14.5" spans="2:9">
+    <row r="6" customFormat="1" ht="14.5" spans="2:9">
       <c r="B6">
         <v>2</v>
       </c>
@@ -1183,14 +1196,14 @@
       <c r="G6">
         <v>200</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" ht="14.5" spans="2:9">
+    <row r="7" customFormat="1" ht="14.5" spans="2:9">
       <c r="B7">
         <v>3</v>
       </c>
@@ -1206,14 +1219,14 @@
       <c r="G7">
         <v>200</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>24</v>
+      <c r="H7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="8" ht="14.5" spans="2:9">
+    <row r="8" customFormat="1" ht="14.5" spans="2:9">
       <c r="B8">
         <v>4</v>
       </c>
@@ -1229,14 +1242,14 @@
       <c r="G8">
         <v>200</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>24</v>
+      <c r="H8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="9" ht="14.5" spans="2:9">
+    <row r="9" customFormat="1" ht="14.5" spans="2:9">
       <c r="B9">
         <v>5</v>
       </c>
@@ -1252,14 +1265,14 @@
       <c r="G9">
         <v>200</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>24</v>
+      <c r="H9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="10" ht="14.5" spans="2:9">
+    <row r="10" customFormat="1" ht="14.5" spans="2:9">
       <c r="B10">
         <v>6</v>
       </c>
@@ -1278,7 +1291,7 @@
       <c r="H10">
         <v>1</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="3">
         <v>4</v>
       </c>
     </row>
